--- a/shemas-word/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/shemas-word/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:25:21+00:00</t>
+    <t>2026-06-18T08:26:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
